--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.83323199130594</v>
+        <v>6.310400198587216</v>
       </c>
       <c r="D2" t="n">
-        <v>40.90339015706376</v>
+        <v>6.646800900522861</v>
       </c>
       <c r="E2" t="n">
-        <v>11.15832585784801</v>
+        <v>1.813227951900302</v>
       </c>
       <c r="F2" t="n">
-        <v>10.60123242495435</v>
+        <v>1.722700269055081</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.68153589088222</v>
+        <v>6.123249582268362</v>
       </c>
       <c r="D3" t="n">
-        <v>35.59065254321801</v>
+        <v>5.783481038272926</v>
       </c>
       <c r="E3" t="n">
-        <v>11.15832585784801</v>
+        <v>1.813227951900302</v>
       </c>
       <c r="F3" t="n">
-        <v>10.60123242495435</v>
+        <v>1.722700269055081</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.64149060828501</v>
+        <v>8.229242223846315</v>
       </c>
       <c r="D4" t="n">
-        <v>47.75163913471897</v>
+        <v>7.759641359391833</v>
       </c>
       <c r="E4" t="n">
-        <v>11.15832585784801</v>
+        <v>1.813227951900302</v>
       </c>
       <c r="F4" t="n">
-        <v>10.60123242495435</v>
+        <v>1.722700269055081</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.8180791892614</v>
+        <v>7.770437868254978</v>
       </c>
       <c r="D5" t="n">
-        <v>44.86099175125694</v>
+        <v>7.289911159579253</v>
       </c>
       <c r="E5" t="n">
-        <v>11.15832585784801</v>
+        <v>1.813227951900302</v>
       </c>
       <c r="F5" t="n">
-        <v>10.60123242495435</v>
+        <v>1.722700269055081</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.82802136601372</v>
+        <v>9.55955347197723</v>
       </c>
       <c r="D6" t="n">
-        <v>56.71829758088911</v>
+        <v>9.216723356894482</v>
       </c>
       <c r="E6" t="n">
-        <v>11.15832585784801</v>
+        <v>1.813227951900302</v>
       </c>
       <c r="F6" t="n">
-        <v>10.60123242495435</v>
+        <v>1.722700269055081</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>69.73805953018316</v>
+        <v>11.33243467365476</v>
       </c>
       <c r="D7" t="n">
-        <v>67.72758764473329</v>
+        <v>11.00573299226916</v>
       </c>
       <c r="E7" t="n">
-        <v>11.15832585784801</v>
+        <v>1.813227951900302</v>
       </c>
       <c r="F7" t="n">
-        <v>10.60123242495435</v>
+        <v>1.722700269055081</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
